--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123689960</v>
+        <v>123689964</v>
       </c>
       <c r="B2" t="n">
-        <v>91317</v>
+        <v>91001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2063</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>767805</v>
+        <v>767806</v>
       </c>
       <c r="R2" t="n">
-        <v>7072953</v>
+        <v>7072964</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,11 +753,6 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,12 +774,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies # Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123689949</v>
+        <v>123689966</v>
       </c>
       <c r="B3" t="n">
-        <v>90966</v>
+        <v>91001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767799</v>
+        <v>767806</v>
       </c>
       <c r="R3" t="n">
-        <v>7072891</v>
+        <v>7072952</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -901,12 +896,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt rötad</t>
+          <t>Grov gran, levande</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt rötad</t>
+          <t>Picea abies # Grov gran, levande</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -924,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123689966</v>
+        <v>123689959</v>
       </c>
       <c r="B4" t="n">
-        <v>90984</v>
+        <v>91001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -964,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>767806</v>
+        <v>767805</v>
       </c>
       <c r="R4" t="n">
-        <v>7072952</v>
+        <v>7072953</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1002,6 +997,11 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Grov gran, levande</t>
+          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Grov gran, levande</t>
+          <t>Picea abies # Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123689964</v>
+        <v>123689949</v>
       </c>
       <c r="B5" t="n">
-        <v>90984</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,21 +1062,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>767806</v>
+        <v>767799</v>
       </c>
       <c r="R5" t="n">
-        <v>7072964</v>
+        <v>7072891</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt</t>
+          <t>Granlåga, knäckt rötad</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
+          <t>Picea abies # Granlåga, knäckt rötad</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123689959</v>
+        <v>123689960</v>
       </c>
       <c r="B6" t="n">
-        <v>90984</v>
+        <v>91334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1180,25 +1180,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123689964</v>
+        <v>123689959</v>
       </c>
       <c r="B2" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>767806</v>
+        <v>767805</v>
       </c>
       <c r="R2" t="n">
-        <v>7072964</v>
+        <v>7072953</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,6 +753,11 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,12 +779,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt</t>
+          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
+          <t>Picea abies # Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123689966</v>
+        <v>123689949</v>
       </c>
       <c r="B3" t="n">
-        <v>91001</v>
+        <v>90988</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,21 +818,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767806</v>
+        <v>767799</v>
       </c>
       <c r="R3" t="n">
-        <v>7072952</v>
+        <v>7072891</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -896,12 +901,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Grov gran, levande</t>
+          <t>Granlåga, knäckt rötad</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Grov gran, levande</t>
+          <t>Picea abies # Granlåga, knäckt rötad</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123689959</v>
+        <v>123689964</v>
       </c>
       <c r="B4" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -959,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>767805</v>
+        <v>767806</v>
       </c>
       <c r="R4" t="n">
-        <v>7072953</v>
+        <v>7072964</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,11 +1002,6 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123689949</v>
+        <v>123689966</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>91006</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,21 +1062,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>767799</v>
+        <v>767806</v>
       </c>
       <c r="R5" t="n">
-        <v>7072891</v>
+        <v>7072952</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt rötad</t>
+          <t>Grov gran, levande</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt rötad</t>
+          <t>Picea abies # Grov gran, levande</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1171,7 +1171,7 @@
         <v>123689960</v>
       </c>
       <c r="B6" t="n">
-        <v>91334</v>
+        <v>91339</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123689959</v>
+        <v>123689964</v>
       </c>
       <c r="B2" t="n">
-        <v>91006</v>
+        <v>91008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>767805</v>
+        <v>767806</v>
       </c>
       <c r="R2" t="n">
-        <v>7072953</v>
+        <v>7072964</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,11 +753,6 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,12 +774,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies # Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,7 +800,7 @@
         <v>123689949</v>
       </c>
       <c r="B3" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -924,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123689964</v>
+        <v>123689959</v>
       </c>
       <c r="B4" t="n">
-        <v>91006</v>
+        <v>91008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -964,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>767806</v>
+        <v>767805</v>
       </c>
       <c r="R4" t="n">
-        <v>7072964</v>
+        <v>7072953</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1002,6 +997,11 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt</t>
+          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
+          <t>Picea abies # Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1049,7 +1049,7 @@
         <v>123689966</v>
       </c>
       <c r="B5" t="n">
-        <v>91006</v>
+        <v>91008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>123689960</v>
       </c>
       <c r="B6" t="n">
-        <v>91339</v>
+        <v>91341</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123689964</v>
+        <v>123689960</v>
       </c>
       <c r="B2" t="n">
-        <v>91008</v>
+        <v>91341</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>767806</v>
+        <v>767805</v>
       </c>
       <c r="R2" t="n">
-        <v>7072964</v>
+        <v>7072953</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,6 +753,11 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,12 +779,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt</t>
+          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
+          <t>Picea abies # Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123689949</v>
+        <v>123689964</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>91008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,21 +818,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767799</v>
+        <v>767806</v>
       </c>
       <c r="R3" t="n">
-        <v>7072891</v>
+        <v>7072964</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -896,12 +901,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt rötad</t>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt rötad</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,7 +924,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123689959</v>
+        <v>123689966</v>
       </c>
       <c r="B4" t="n">
         <v>91008</v>
@@ -959,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>767805</v>
+        <v>767806</v>
       </c>
       <c r="R4" t="n">
-        <v>7072953</v>
+        <v>7072952</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,11 +1002,6 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+          <t>Grov gran, levande</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+          <t>Picea abies # Grov gran, levande</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1046,7 +1046,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123689966</v>
+        <v>123689959</v>
       </c>
       <c r="B5" t="n">
         <v>91008</v>
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>767806</v>
+        <v>767805</v>
       </c>
       <c r="R5" t="n">
-        <v>7072952</v>
+        <v>7072953</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1124,6 +1124,11 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1145,12 +1150,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Grov gran, levande</t>
+          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Grov gran, levande</t>
+          <t>Picea abies # Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1168,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123689960</v>
+        <v>123689949</v>
       </c>
       <c r="B6" t="n">
-        <v>91341</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1180,25 +1185,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2063</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1208,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>767805</v>
+        <v>767799</v>
       </c>
       <c r="R6" t="n">
-        <v>7072953</v>
+        <v>7072891</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1246,11 +1251,6 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+          <t>Granlåga, knäckt rötad</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+          <t>Picea abies # Granlåga, knäckt rötad</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123689960</v>
+        <v>123689959</v>
       </c>
       <c r="B2" t="n">
-        <v>91341</v>
+        <v>91008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2063</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123689964</v>
+        <v>123689949</v>
       </c>
       <c r="B3" t="n">
-        <v>91008</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,21 +818,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767806</v>
+        <v>767799</v>
       </c>
       <c r="R3" t="n">
-        <v>7072964</v>
+        <v>7072891</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt</t>
+          <t>Granlåga, knäckt rötad</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
+          <t>Picea abies # Granlåga, knäckt rötad</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -924,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123689966</v>
+        <v>123689960</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>91341</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,25 +936,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>767806</v>
+        <v>767805</v>
       </c>
       <c r="R4" t="n">
-        <v>7072952</v>
+        <v>7072953</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1002,6 +1002,11 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1023,12 +1028,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Grov gran, levande</t>
+          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Grov gran, levande</t>
+          <t>Picea abies # Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1046,7 +1051,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123689959</v>
+        <v>123689964</v>
       </c>
       <c r="B5" t="n">
         <v>91008</v>
@@ -1086,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>767805</v>
+        <v>767806</v>
       </c>
       <c r="R5" t="n">
-        <v>7072953</v>
+        <v>7072964</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1124,11 +1129,6 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123689949</v>
+        <v>123689966</v>
       </c>
       <c r="B6" t="n">
-        <v>90990</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,21 +1189,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>767799</v>
+        <v>767806</v>
       </c>
       <c r="R6" t="n">
-        <v>7072891</v>
+        <v>7072952</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt rötad</t>
+          <t>Grov gran, levande</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt rötad</t>
+          <t>Picea abies # Grov gran, levande</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123689959</v>
+        <v>123689966</v>
       </c>
       <c r="B2" t="n">
         <v>91008</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>767805</v>
+        <v>767806</v>
       </c>
       <c r="R2" t="n">
-        <v>7072953</v>
+        <v>7072952</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,11 +753,6 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,12 +774,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+          <t>Grov gran, levande</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies # Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+          <t>Picea abies # Grov gran, levande</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123689949</v>
+        <v>123689964</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>91008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767799</v>
+        <v>767806</v>
       </c>
       <c r="R3" t="n">
-        <v>7072891</v>
+        <v>7072964</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -901,12 +896,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt rötad</t>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt rötad</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1051,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123689964</v>
+        <v>123689949</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,21 +1062,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1091,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>767806</v>
+        <v>767799</v>
       </c>
       <c r="R5" t="n">
-        <v>7072964</v>
+        <v>7072891</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1150,12 +1145,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt</t>
+          <t>Granlåga, knäckt rötad</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
+          <t>Picea abies # Granlåga, knäckt rötad</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1173,7 +1168,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123689966</v>
+        <v>123689959</v>
       </c>
       <c r="B6" t="n">
         <v>91008</v>
@@ -1213,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>767806</v>
+        <v>767805</v>
       </c>
       <c r="R6" t="n">
-        <v>7072952</v>
+        <v>7072953</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1251,6 +1246,11 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Grov gran, levande</t>
+          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Grov gran, levande</t>
+          <t>Picea abies # Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123689966</v>
+        <v>123689949</v>
       </c>
       <c r="B2" t="n">
-        <v>91008</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>767806</v>
+        <v>767799</v>
       </c>
       <c r="R2" t="n">
-        <v>7072952</v>
+        <v>7072891</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -774,12 +774,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Grov gran, levande</t>
+          <t>Granlåga, knäckt rötad</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies # Grov gran, levande</t>
+          <t>Picea abies # Granlåga, knäckt rötad</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123689964</v>
+        <v>123689966</v>
       </c>
       <c r="B3" t="n">
         <v>91008</v>
@@ -840,7 +840,7 @@
         <v>767806</v>
       </c>
       <c r="R3" t="n">
-        <v>7072964</v>
+        <v>7072952</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -896,12 +896,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt</t>
+          <t>Grov gran, levande</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
+          <t>Picea abies # Grov gran, levande</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123689949</v>
+        <v>123689959</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>91008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,21 +1062,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>767799</v>
+        <v>767805</v>
       </c>
       <c r="R5" t="n">
-        <v>7072891</v>
+        <v>7072953</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1124,6 +1124,11 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1145,12 +1150,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt rötad</t>
+          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt rötad</t>
+          <t>Picea abies # Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1168,7 +1173,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123689959</v>
+        <v>123689964</v>
       </c>
       <c r="B6" t="n">
         <v>91008</v>
@@ -1208,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>767805</v>
+        <v>767806</v>
       </c>
       <c r="R6" t="n">
-        <v>7072953</v>
+        <v>7072964</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1246,11 +1251,6 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123689949</v>
+        <v>123689959</v>
       </c>
       <c r="B2" t="n">
-        <v>90990</v>
+        <v>91008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>767799</v>
+        <v>767805</v>
       </c>
       <c r="R2" t="n">
-        <v>7072891</v>
+        <v>7072953</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,6 +753,11 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,12 +779,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt rötad</t>
+          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt rötad</t>
+          <t>Picea abies # Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123689966</v>
+        <v>123689964</v>
       </c>
       <c r="B3" t="n">
         <v>91008</v>
@@ -840,7 +845,7 @@
         <v>767806</v>
       </c>
       <c r="R3" t="n">
-        <v>7072952</v>
+        <v>7072964</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -896,12 +901,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Grov gran, levande</t>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Grov gran, levande</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123689960</v>
+        <v>123689949</v>
       </c>
       <c r="B4" t="n">
-        <v>91341</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,25 +936,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2063</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>767805</v>
+        <v>767799</v>
       </c>
       <c r="R4" t="n">
-        <v>7072953</v>
+        <v>7072891</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,11 +1002,6 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+          <t>Granlåga, knäckt rötad</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Mossbevuxen äldre grov granlåga. Flera fina lågor i närområdet</t>
+          <t>Picea abies # Granlåga, knäckt rötad</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123689959</v>
+        <v>123689960</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>91341</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,25 +1058,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1173,7 +1173,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123689964</v>
+        <v>123689966</v>
       </c>
       <c r="B6" t="n">
         <v>91008</v>
@@ -1216,7 +1216,7 @@
         <v>767806</v>
       </c>
       <c r="R6" t="n">
-        <v>7072964</v>
+        <v>7072952</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt</t>
+          <t>Grov gran, levande</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
+          <t>Picea abies # Grov gran, levande</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1395,6 +1395,230 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125424536</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bastuskäret, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>767792</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7072919</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125424535</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56492</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bastuskäret, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>767774</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7072937</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1397,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125424536</v>
+        <v>125424535</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>56492</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,21 +1413,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>208260</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>767792</v>
+        <v>767774</v>
       </c>
       <c r="R8" t="n">
-        <v>7072919</v>
+        <v>7072937</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125424535</v>
+        <v>125424536</v>
       </c>
       <c r="B9" t="n">
-        <v>56492</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,21 +1525,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208260</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767774</v>
+        <v>767792</v>
       </c>
       <c r="R9" t="n">
-        <v>7072937</v>
+        <v>7072919</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,6 +1618,132 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123689957</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91410</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bastuskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>767822</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7072937</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Del av granstam hängande på annan gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Del av granstam hängande på annan gran</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies # Del av granstam hängande på annan gran</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Roger Olofsson, Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1397,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125424535</v>
+        <v>125424536</v>
       </c>
       <c r="B8" t="n">
-        <v>56492</v>
+        <v>91131</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,21 +1413,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208260</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>767774</v>
+        <v>767792</v>
       </c>
       <c r="R8" t="n">
-        <v>7072937</v>
+        <v>7072919</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125424536</v>
+        <v>125424535</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>56606</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,21 +1525,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>208260</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767792</v>
+        <v>767774</v>
       </c>
       <c r="R9" t="n">
-        <v>7072919</v>
+        <v>7072937</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,7 +1624,7 @@
         <v>123689957</v>
       </c>
       <c r="B10" t="n">
-        <v>91410</v>
+        <v>91570</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1397,15 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125424536</v>
+        <v>125424535</v>
       </c>
       <c r="B8" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56607</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,21 +1408,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>208260</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1437,10 +1432,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>767792</v>
+        <v>767774</v>
       </c>
       <c r="R8" t="n">
-        <v>7072919</v>
+        <v>7072937</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1472,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,7 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,15 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125424535</v>
+        <v>125424536</v>
       </c>
       <c r="B9" t="n">
-        <v>56606</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,21 +1515,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208260</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1549,10 +1539,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767774</v>
+        <v>767792</v>
       </c>
       <c r="R9" t="n">
-        <v>7072937</v>
+        <v>7072919</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1584,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,12 +1614,7 @@
         <v>123689957</v>
       </c>
       <c r="B10" t="n">
-        <v>91570</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91624</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1507,7 +1507,7 @@
         <v>125424536</v>
       </c>
       <c r="B9" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>123689957</v>
       </c>
       <c r="B10" t="n">
-        <v>91624</v>
+        <v>91631</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1507,7 +1507,7 @@
         <v>125424536</v>
       </c>
       <c r="B9" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>123689957</v>
       </c>
       <c r="B10" t="n">
-        <v>91631</v>
+        <v>91635</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1507,7 +1507,7 @@
         <v>125424536</v>
       </c>
       <c r="B9" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>123689957</v>
       </c>
       <c r="B10" t="n">
-        <v>91635</v>
+        <v>91639</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1614,7 +1614,7 @@
         <v>123689957</v>
       </c>
       <c r="B10" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1730,6 +1730,362 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127804562</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91701</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bastuskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>767807</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7072959</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Granticka på denna granlåga, med GTP</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Granlåga, grov och mossbevuxen</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga, grov och mossbevuxen</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127804542</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92029</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bastuskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>767803</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7072963</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Granhögstubbe med granticka</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe med granticka</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127804600</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91350</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bastuskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>767794</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7072967</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>granlåga knäckt hela lågan. delvis i mossan</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga knäckt hela lågan. delvis i mossan</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1732,32 +1732,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127804562</v>
+        <v>127804542</v>
       </c>
       <c r="B11" t="n">
-        <v>91701</v>
+        <v>92035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1506</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767807</v>
+        <v>767803</v>
       </c>
       <c r="R11" t="n">
-        <v>7072959</v>
+        <v>7072963</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1805,11 +1805,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Granticka på denna granlåga, med GTP</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1831,12 +1826,12 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>Granlåga, grov och mossbevuxen</t>
+          <t>Granhögstubbe med granticka</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, grov och mossbevuxen</t>
+          <t>Picea abies # Granhögstubbe med granticka</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1854,32 +1849,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127804542</v>
+        <v>127804600</v>
       </c>
       <c r="B12" t="n">
-        <v>92029</v>
+        <v>91356</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1889,10 +1884,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767803</v>
+        <v>767794</v>
       </c>
       <c r="R12" t="n">
-        <v>7072963</v>
+        <v>7072967</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1948,12 +1943,12 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>Granhögstubbe med granticka</t>
+          <t>granlåga knäckt hela lågan. delvis i mossan</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe med granticka</t>
+          <t>Picea abies # granlåga knäckt hela lågan. delvis i mossan</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1971,45 +1966,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127804600</v>
+        <v>127804562</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>91710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1505</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>767794</v>
+        <v>767807</v>
       </c>
       <c r="R13" t="n">
-        <v>7072967</v>
+        <v>7072959</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2044,12 +2042,18 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Granticka på denna granlåga, med GTP</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2065,12 +2069,12 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>granlåga knäckt hela lågan. delvis i mossan</t>
+          <t>Granlåga, grov och mossbevuxen</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga knäckt hela lågan. delvis i mossan</t>
+          <t>Picea abies # Granlåga, grov och mossbevuxen</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1735,7 +1735,7 @@
         <v>127804542</v>
       </c>
       <c r="B11" t="n">
-        <v>92035</v>
+        <v>92038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>127804600</v>
       </c>
       <c r="B12" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>127804562</v>
       </c>
       <c r="B13" t="n">
-        <v>91710</v>
+        <v>91713</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1735,7 +1735,7 @@
         <v>127804542</v>
       </c>
       <c r="B11" t="n">
-        <v>92038</v>
+        <v>92046</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>127804600</v>
       </c>
       <c r="B12" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>127804562</v>
       </c>
       <c r="B13" t="n">
-        <v>91713</v>
+        <v>91721</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1735,7 +1735,7 @@
         <v>127804542</v>
       </c>
       <c r="B11" t="n">
-        <v>92046</v>
+        <v>92047</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>127804600</v>
       </c>
       <c r="B12" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>127804562</v>
       </c>
       <c r="B13" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1735,7 +1735,7 @@
         <v>127804542</v>
       </c>
       <c r="B11" t="n">
-        <v>92047</v>
+        <v>92048</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>127804600</v>
       </c>
       <c r="B12" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>127804562</v>
       </c>
       <c r="B13" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1735,7 +1735,7 @@
         <v>127804542</v>
       </c>
       <c r="B11" t="n">
-        <v>92048</v>
+        <v>92049</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>127804600</v>
       </c>
       <c r="B12" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>127804562</v>
       </c>
       <c r="B13" t="n">
-        <v>91723</v>
+        <v>91724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1735,7 +1735,7 @@
         <v>127804542</v>
       </c>
       <c r="B11" t="n">
-        <v>92049</v>
+        <v>92057</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>127804600</v>
       </c>
       <c r="B12" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>127804562</v>
       </c>
       <c r="B13" t="n">
-        <v>91724</v>
+        <v>91732</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1735,7 +1735,7 @@
         <v>127804542</v>
       </c>
       <c r="B11" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>127804600</v>
       </c>
       <c r="B12" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>127804562</v>
       </c>
       <c r="B13" t="n">
-        <v>91732</v>
+        <v>91812</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,21 +1977,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1505</v>
+        <v>2063</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Granticka på denna granlåga, med GTP</t>
+          <t>Granticka på denna granlåga, med GTP. Artbestämd mha mikroskopering av Gudrun Norstedt</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1969,7 +1969,7 @@
         <v>127804562</v>
       </c>
       <c r="B13" t="n">
-        <v>91812</v>
+        <v>91818</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1969,7 +1969,7 @@
         <v>127804562</v>
       </c>
       <c r="B13" t="n">
-        <v>91818</v>
+        <v>91824</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1969,7 +1969,7 @@
         <v>127804562</v>
       </c>
       <c r="B13" t="n">
-        <v>91824</v>
+        <v>91826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1969,7 +1969,7 @@
         <v>127804562</v>
       </c>
       <c r="B13" t="n">
-        <v>91826</v>
+        <v>91827</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1969,7 +1969,7 @@
         <v>127804562</v>
       </c>
       <c r="B13" t="n">
-        <v>91827</v>
+        <v>91854</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1969,7 +1969,7 @@
         <v>127804562</v>
       </c>
       <c r="B13" t="n">
-        <v>91854</v>
+        <v>91859</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1969,7 +1969,7 @@
         <v>127804562</v>
       </c>
       <c r="B13" t="n">
-        <v>91859</v>
+        <v>91864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1969,7 +1969,7 @@
         <v>127804562</v>
       </c>
       <c r="B13" t="n">
-        <v>91864</v>
+        <v>91868</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1969,7 +1969,7 @@
         <v>127804562</v>
       </c>
       <c r="B13" t="n">
-        <v>91868</v>
+        <v>91873</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1969,7 +1969,7 @@
         <v>127804562</v>
       </c>
       <c r="B13" t="n">
-        <v>91876</v>
+        <v>91881</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11780-2025 artfynd.xlsx
+++ b/artfynd/A 11780-2025 artfynd.xlsx
@@ -1969,7 +1969,7 @@
         <v>127804562</v>
       </c>
       <c r="B13" t="n">
-        <v>91881</v>
+        <v>91887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
